--- a/samples/wildling/기획데이터/Monster.xlsx
+++ b/samples/wildling/기획데이터/Monster.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1649" uniqueCount="498">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1664" uniqueCount="508">
   <si>
     <t xml:space="preserve">:table Monster</t>
   </si>
@@ -171,6 +171,21 @@
     <t xml:space="preserve">1레벨 기준 능력치</t>
   </si>
   <si>
+    <t xml:space="preserve">공격</t>
+  </si>
+  <si>
+    <t xml:space="preserve">방어</t>
+  </si>
+  <si>
+    <t xml:space="preserve">행동 순서</t>
+  </si>
+  <si>
+    <t xml:space="preserve">치명타 확률. 만분율</t>
+  </si>
+  <si>
+    <t xml:space="preserve">치명타 배수. 만분율</t>
+  </si>
+  <si>
     <t xml:space="preserve">서식 지역 플래그</t>
   </si>
   <si>
@@ -1399,6 +1414,21 @@
   </si>
   <si>
     <t xml:space="preserve">각성으로 더해지는 값</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격 증가분</t>
+  </si>
+  <si>
+    <t xml:space="preserve">방어 증가분</t>
+  </si>
+  <si>
+    <t xml:space="preserve">행동 순서 증가분</t>
+  </si>
+  <si>
+    <t xml:space="preserve">치명타 확률 증가분</t>
+  </si>
+  <si>
+    <t xml:space="preserve">치명타 배수 증가분</t>
   </si>
   <si>
     <t xml:space="preserve">각성 조건</t>
@@ -1939,115 +1969,135 @@
       <c r="K4" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="L4" s="4"/>
-      <c r="M4" s="4"/>
-      <c r="N4" s="4"/>
-      <c r="O4" s="4"/>
-      <c r="P4" s="4"/>
+      <c r="L4" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="M4" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="N4" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="O4" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="P4" s="4" t="s">
+        <v>54</v>
+      </c>
       <c r="Q4" s="4" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="R4" s="4" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="S4" s="4" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="U4" s="4" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="V4" s="4" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="W4" s="4"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="L5" s="4"/>
-      <c r="M5" s="4"/>
-      <c r="N5" s="4"/>
-      <c r="O5" s="4"/>
-      <c r="P5" s="4"/>
+        <v>62</v>
+      </c>
+      <c r="L5" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="M5" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="N5" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="O5" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="P5" s="4" t="s">
+        <v>62</v>
+      </c>
       <c r="Q5" s="4" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="R5" s="4" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="S5" s="4" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="U5" s="4" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="V5" s="4"/>
       <c r="W5" s="4"/>
     </row>
     <row r="6">
       <c r="B6" s="6" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="E6" s="6">
         <v>1</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="K6" s="6">
         <v>420</v>
@@ -2068,48 +2118,48 @@
         <v>15000</v>
       </c>
       <c r="Q6" s="6" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="R6" s="6">
         <v>3</v>
       </c>
       <c r="S6" s="6" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="T6" s="6" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="U6" s="6" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
     </row>
     <row r="7">
       <c r="B7" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="E7" s="7">
+        <v>2</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I7" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="J7" s="7" t="s">
         <v>71</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="E7" s="7">
-        <v>2</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="G7" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="H7" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="I7" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="J7" s="7" t="s">
-        <v>66</v>
       </c>
       <c r="K7" s="7">
         <v>756</v>
@@ -2130,48 +2180,48 @@
         <v>15000</v>
       </c>
       <c r="Q7" s="7" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="R7" s="7">
         <v>3</v>
       </c>
       <c r="S7" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="T7" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="T7" s="7" t="s">
-        <v>69</v>
-      </c>
       <c r="U7" s="7" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="6" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="E8" s="6">
         <v>3</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="K8" s="6">
         <v>1331</v>
@@ -2192,48 +2242,48 @@
         <v>15000</v>
       </c>
       <c r="Q8" s="6" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="R8" s="6">
         <v>3</v>
       </c>
       <c r="S8" s="6" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="T8" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="U8" s="6" t="s">
         <v>80</v>
-      </c>
-      <c r="U8" s="6" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="9">
       <c r="B9" s="7" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="E9" s="7">
         <v>1</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="K9" s="7">
         <v>340</v>
@@ -2254,48 +2304,48 @@
         <v>15000</v>
       </c>
       <c r="Q9" s="7" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="R9" s="7">
         <v>1</v>
       </c>
       <c r="S9" s="7" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="T9" s="7" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="U9" s="7" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
     </row>
     <row r="10">
       <c r="B10" s="6" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="E10" s="6">
         <v>1</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="K10" s="6">
         <v>322</v>
@@ -2316,48 +2366,48 @@
         <v>17000</v>
       </c>
       <c r="Q10" s="6" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="R10" s="6">
         <v>2</v>
       </c>
       <c r="S10" s="6" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="T10" s="6" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="U10" s="6" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
     </row>
     <row r="11">
       <c r="B11" s="7" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="C11" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="E11" s="7">
+        <v>2</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="H11" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I11" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="D11" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="E11" s="7">
-        <v>2</v>
-      </c>
-      <c r="F11" s="7" t="s">
+      <c r="J11" s="7" t="s">
         <v>98</v>
-      </c>
-      <c r="G11" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="H11" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="I11" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="J11" s="7" t="s">
-        <v>93</v>
       </c>
       <c r="K11" s="7">
         <v>580</v>
@@ -2378,48 +2428,48 @@
         <v>17000</v>
       </c>
       <c r="Q11" s="7" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="R11" s="7">
         <v>2</v>
       </c>
       <c r="S11" s="7" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="T11" s="7" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="U11" s="7" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="6" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="E12" s="6">
         <v>1</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="K12" s="6">
         <v>483</v>
@@ -2440,48 +2490,48 @@
         <v>15000</v>
       </c>
       <c r="Q12" s="6" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="R12" s="6">
         <v>2</v>
       </c>
       <c r="S12" s="6" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="T12" s="6" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="U12" s="6" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="7" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="C13" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="D13" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="D13" s="7" t="s">
-        <v>103</v>
-      </c>
       <c r="E13" s="7">
         <v>2</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="I13" s="7" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="J13" s="7" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="K13" s="7">
         <v>869</v>
@@ -2502,48 +2552,48 @@
         <v>15000</v>
       </c>
       <c r="Q13" s="7" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="R13" s="7">
         <v>2</v>
       </c>
       <c r="S13" s="7" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="T13" s="7" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="U13" s="7" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="6" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="E14" s="6">
         <v>1</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="K14" s="6">
         <v>396</v>
@@ -2564,48 +2614,48 @@
         <v>15000</v>
       </c>
       <c r="Q14" s="6" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="R14" s="6">
         <v>1</v>
       </c>
       <c r="S14" s="6" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="T14" s="6" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="U14" s="6" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="7" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="E15" s="7">
         <v>1</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="I15" s="7" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="K15" s="7">
         <v>517</v>
@@ -2626,48 +2676,48 @@
         <v>15000</v>
       </c>
       <c r="Q15" s="7" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="R15" s="7">
         <v>2</v>
       </c>
       <c r="S15" s="7" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="T15" s="7" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="U15" s="7" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="D16" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="C16" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>123</v>
-      </c>
       <c r="E16" s="6">
         <v>2</v>
       </c>
       <c r="F16" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="G16" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="H16" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="I16" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="G16" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="H16" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I16" s="6" t="s">
-        <v>125</v>
-      </c>
       <c r="J16" s="6" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="K16" s="6">
         <v>930</v>
@@ -2688,48 +2738,48 @@
         <v>15000</v>
       </c>
       <c r="Q16" s="6" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="R16" s="6">
         <v>2</v>
       </c>
       <c r="S16" s="6" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="T16" s="6" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="U16" s="6" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="7" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="E17" s="7">
         <v>1</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="I17" s="7" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="J17" s="7" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="K17" s="7">
         <v>322</v>
@@ -2750,48 +2800,48 @@
         <v>17000</v>
       </c>
       <c r="Q17" s="7" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="R17" s="7">
         <v>3</v>
       </c>
       <c r="S17" s="7" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="T17" s="7" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="U17" s="7" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="E18" s="6">
+        <v>2</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="G18" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="C18" s="6" t="s">
+      <c r="H18" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="D18" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="E18" s="6">
-        <v>2</v>
-      </c>
-      <c r="F18" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="G18" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="H18" s="6" t="s">
-        <v>138</v>
-      </c>
       <c r="I18" s="6" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="J18" s="6" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="K18" s="6">
         <v>580</v>
@@ -2812,48 +2862,48 @@
         <v>17000</v>
       </c>
       <c r="Q18" s="6" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="R18" s="6">
         <v>3</v>
       </c>
       <c r="S18" s="6" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="T18" s="6" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="U18" s="6" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="7" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="E19" s="7">
         <v>3</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="I19" s="7" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="J19" s="7" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="K19" s="7">
         <v>1021</v>
@@ -2874,48 +2924,48 @@
         <v>17000</v>
       </c>
       <c r="Q19" s="7" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="R19" s="7">
         <v>3</v>
       </c>
       <c r="S19" s="7" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="T19" s="7" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="U19" s="7" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="6" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="E20" s="6">
         <v>1</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="J20" s="6" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="K20" s="6">
         <v>280</v>
@@ -2936,48 +2986,48 @@
         <v>17000</v>
       </c>
       <c r="Q20" s="6" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="R20" s="6">
         <v>1</v>
       </c>
       <c r="S20" s="6" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="T20" s="6" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="U20" s="6" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
     </row>
     <row r="21">
       <c r="B21" s="7" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="E21" s="7">
         <v>1</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="I21" s="7" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="J21" s="7" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="K21" s="7">
         <v>420</v>
@@ -2998,48 +3048,48 @@
         <v>15000</v>
       </c>
       <c r="Q21" s="7" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="R21" s="7">
         <v>2</v>
       </c>
       <c r="S21" s="7" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="T21" s="7" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="U21" s="7" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
     </row>
     <row r="22">
       <c r="B22" s="6" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="C22" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="D22" s="6" t="s">
         <v>164</v>
       </c>
-      <c r="D22" s="6" t="s">
-        <v>159</v>
-      </c>
       <c r="E22" s="6">
         <v>2</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="I22" s="6" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="J22" s="6" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="K22" s="6">
         <v>756</v>
@@ -3060,48 +3110,48 @@
         <v>15000</v>
       </c>
       <c r="Q22" s="6" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="R22" s="6">
         <v>2</v>
       </c>
       <c r="S22" s="6" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="T22" s="6" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="U22" s="6" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="7" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="E23" s="7">
         <v>1</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="H23" s="7" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="I23" s="7" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="J23" s="7" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="K23" s="7">
         <v>322</v>
@@ -3122,48 +3172,48 @@
         <v>17000</v>
       </c>
       <c r="Q23" s="7" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="R23" s="7">
         <v>1</v>
       </c>
       <c r="S23" s="7" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="T23" s="7" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="U23" s="7" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="6" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="E24" s="6">
         <v>1</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="I24" s="6" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="J24" s="6" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="K24" s="6">
         <v>554</v>
@@ -3184,48 +3234,48 @@
         <v>15000</v>
       </c>
       <c r="Q24" s="6" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="R24" s="6">
         <v>2</v>
       </c>
       <c r="S24" s="6" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="T24" s="6" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="U24" s="6" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
     </row>
     <row r="25">
       <c r="B25" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="D25" s="7" t="s">
         <v>181</v>
       </c>
-      <c r="C25" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="D25" s="7" t="s">
-        <v>176</v>
-      </c>
       <c r="E25" s="7">
         <v>2</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="H25" s="7" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="I25" s="7" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="J25" s="7" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="K25" s="7">
         <v>998</v>
@@ -3246,48 +3296,48 @@
         <v>15000</v>
       </c>
       <c r="Q25" s="7" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="R25" s="7">
         <v>2</v>
       </c>
       <c r="S25" s="7" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="T25" s="7" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="U25" s="7" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
     </row>
     <row r="26">
       <c r="B26" s="6" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="E26" s="6">
         <v>1</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="I26" s="6" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="J26" s="6" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="K26" s="6">
         <v>426</v>
@@ -3308,48 +3358,48 @@
         <v>17000</v>
       </c>
       <c r="Q26" s="6" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="R26" s="6">
         <v>1</v>
       </c>
       <c r="S26" s="6" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="T26" s="6" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="U26" s="6" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
     </row>
     <row r="27">
       <c r="B27" s="7" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="E27" s="7">
         <v>1</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="G27" s="7" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="H27" s="7" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="I27" s="7" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="J27" s="7" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="K27" s="7">
         <v>396</v>
@@ -3370,48 +3420,48 @@
         <v>15000</v>
       </c>
       <c r="Q27" s="7" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="R27" s="7">
         <v>3</v>
       </c>
       <c r="S27" s="7" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="T27" s="7" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="U27" s="7" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
     </row>
     <row r="28">
       <c r="B28" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="E28" s="6">
+        <v>2</v>
+      </c>
+      <c r="F28" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="G28" s="6" t="s">
         <v>201</v>
       </c>
-      <c r="C28" s="6" t="s">
+      <c r="H28" s="6" t="s">
         <v>202</v>
       </c>
-      <c r="D28" s="6" t="s">
-        <v>194</v>
-      </c>
-      <c r="E28" s="6">
-        <v>2</v>
-      </c>
-      <c r="F28" s="6" t="s">
-        <v>203</v>
-      </c>
-      <c r="G28" s="6" t="s">
-        <v>196</v>
-      </c>
-      <c r="H28" s="6" t="s">
-        <v>197</v>
-      </c>
       <c r="I28" s="6" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="J28" s="6" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="K28" s="6">
         <v>713</v>
@@ -3432,48 +3482,48 @@
         <v>15000</v>
       </c>
       <c r="Q28" s="6" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="R28" s="6">
         <v>3</v>
       </c>
       <c r="S28" s="6" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="T28" s="6" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="U28" s="6" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
     </row>
     <row r="29">
       <c r="B29" s="7" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="E29" s="7">
         <v>3</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="H29" s="7" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="I29" s="7" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="J29" s="7" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="K29" s="7">
         <v>1255</v>
@@ -3494,48 +3544,48 @@
         <v>15000</v>
       </c>
       <c r="Q29" s="7" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="R29" s="7">
         <v>3</v>
       </c>
       <c r="S29" s="7" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="T29" s="7" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="U29" s="7" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
     </row>
     <row r="30">
       <c r="B30" s="6" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="E30" s="6">
         <v>1</v>
       </c>
       <c r="F30" s="6" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="I30" s="6" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="J30" s="6" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="K30" s="6">
         <v>340</v>
@@ -3556,48 +3606,48 @@
         <v>15000</v>
       </c>
       <c r="Q30" s="6" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="R30" s="6">
         <v>1</v>
       </c>
       <c r="S30" s="6" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="T30" s="6" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="U30" s="6" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
     </row>
     <row r="31">
       <c r="B31" s="7" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="E31" s="7">
         <v>1</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="G31" s="7" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="H31" s="7" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="I31" s="7" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="J31" s="7" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="K31" s="7">
         <v>420</v>
@@ -3618,48 +3668,48 @@
         <v>15000</v>
       </c>
       <c r="Q31" s="7" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="R31" s="7">
         <v>2</v>
       </c>
       <c r="S31" s="7" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="T31" s="7" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="U31" s="7" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
     </row>
     <row r="32">
       <c r="B32" s="6" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="C32" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="D32" s="6" t="s">
         <v>225</v>
       </c>
-      <c r="D32" s="6" t="s">
-        <v>220</v>
-      </c>
       <c r="E32" s="6">
         <v>2</v>
       </c>
       <c r="F32" s="6" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="I32" s="6" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="J32" s="6" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="K32" s="6">
         <v>756</v>
@@ -3680,48 +3730,48 @@
         <v>15000</v>
       </c>
       <c r="Q32" s="6" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="R32" s="6">
         <v>2</v>
       </c>
       <c r="S32" s="6" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="T32" s="6" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="U32" s="6" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
     </row>
     <row r="33">
       <c r="B33" s="7" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="E33" s="7">
         <v>1</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="G33" s="7" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="H33" s="7" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="I33" s="7" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="J33" s="7" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="K33" s="7">
         <v>345</v>
@@ -3742,48 +3792,48 @@
         <v>15000</v>
       </c>
       <c r="Q33" s="7" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="R33" s="7">
         <v>1</v>
       </c>
       <c r="S33" s="7" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="T33" s="7" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="U33" s="7" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
     </row>
     <row r="34">
       <c r="B34" s="6" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="E34" s="6">
         <v>1</v>
       </c>
       <c r="F34" s="6" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="I34" s="6" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="J34" s="6" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="K34" s="6">
         <v>322</v>
@@ -3804,48 +3854,48 @@
         <v>17000</v>
       </c>
       <c r="Q34" s="6" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="R34" s="6">
         <v>2</v>
       </c>
       <c r="S34" s="6" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="T34" s="6" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="U34" s="6" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
     </row>
     <row r="35">
       <c r="B35" s="7" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="C35" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="D35" s="7" t="s">
         <v>242</v>
       </c>
-      <c r="D35" s="7" t="s">
-        <v>237</v>
-      </c>
       <c r="E35" s="7">
         <v>2</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="G35" s="7" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="H35" s="7" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="I35" s="7" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="J35" s="7" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="K35" s="7">
         <v>580</v>
@@ -3866,48 +3916,48 @@
         <v>17000</v>
       </c>
       <c r="Q35" s="7" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="R35" s="7">
         <v>2</v>
       </c>
       <c r="S35" s="7" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="T35" s="7" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="U35" s="7" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
     </row>
     <row r="36">
       <c r="B36" s="6" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="E36" s="6">
         <v>1</v>
       </c>
       <c r="F36" s="6" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="I36" s="6" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="J36" s="6" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="K36" s="6">
         <v>638</v>
@@ -3928,48 +3978,48 @@
         <v>15000</v>
       </c>
       <c r="Q36" s="6" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="R36" s="6">
         <v>1</v>
       </c>
       <c r="S36" s="6" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="T36" s="6" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="U36" s="6" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
     </row>
     <row r="37">
       <c r="B37" s="7" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="E37" s="7">
         <v>1</v>
       </c>
       <c r="F37" s="7" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="G37" s="7" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="H37" s="7" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="I37" s="7" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="J37" s="7" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="K37" s="7">
         <v>263</v>
@@ -3990,48 +4040,48 @@
         <v>17000</v>
       </c>
       <c r="Q37" s="7" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="R37" s="7">
         <v>1</v>
       </c>
       <c r="S37" s="7" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="T37" s="7" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="U37" s="7" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
     </row>
     <row r="38">
       <c r="B38" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="C38" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="D38" s="6" t="s">
+        <v>268</v>
+      </c>
+      <c r="E38" s="6">
+        <v>1</v>
+      </c>
+      <c r="F38" s="6" t="s">
+        <v>269</v>
+      </c>
+      <c r="G38" s="6" t="s">
         <v>261</v>
       </c>
-      <c r="C38" s="6" t="s">
+      <c r="H38" s="6" t="s">
         <v>262</v>
       </c>
-      <c r="D38" s="6" t="s">
-        <v>263</v>
-      </c>
-      <c r="E38" s="6">
-        <v>1</v>
-      </c>
-      <c r="F38" s="6" t="s">
-        <v>264</v>
-      </c>
-      <c r="G38" s="6" t="s">
-        <v>256</v>
-      </c>
-      <c r="H38" s="6" t="s">
-        <v>257</v>
-      </c>
       <c r="I38" s="6" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="J38" s="6" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="K38" s="6">
         <v>303</v>
@@ -4052,48 +4102,48 @@
         <v>17000</v>
       </c>
       <c r="Q38" s="6" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="R38" s="6">
         <v>3</v>
       </c>
       <c r="S38" s="6" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="T38" s="6" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="U38" s="6" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
     </row>
     <row r="39">
       <c r="B39" s="7" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="C39" s="7" t="s">
+        <v>273</v>
+      </c>
+      <c r="D39" s="7" t="s">
         <v>268</v>
       </c>
-      <c r="D39" s="7" t="s">
-        <v>263</v>
-      </c>
       <c r="E39" s="7">
         <v>2</v>
       </c>
       <c r="F39" s="7" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="G39" s="7" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="H39" s="7" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="I39" s="7" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="J39" s="7" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="K39" s="7">
         <v>545</v>
@@ -4114,48 +4164,48 @@
         <v>17000</v>
       </c>
       <c r="Q39" s="7" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="R39" s="7">
         <v>3</v>
       </c>
       <c r="S39" s="7" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="T39" s="7" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="U39" s="7" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
     </row>
     <row r="40">
       <c r="B40" s="6" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="E40" s="6">
         <v>3</v>
       </c>
       <c r="F40" s="6" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="I40" s="6" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="J40" s="6" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="K40" s="6">
         <v>959</v>
@@ -4176,48 +4226,48 @@
         <v>17000</v>
       </c>
       <c r="Q40" s="6" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="R40" s="6">
         <v>3</v>
       </c>
       <c r="S40" s="6" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="T40" s="6" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="U40" s="6" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
     </row>
     <row r="41">
       <c r="B41" s="7" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="D41" s="7" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="E41" s="7">
         <v>1</v>
       </c>
       <c r="F41" s="7" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="G41" s="7" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="H41" s="7" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="I41" s="7" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="J41" s="7" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="K41" s="7">
         <v>324</v>
@@ -4238,48 +4288,48 @@
         <v>15000</v>
       </c>
       <c r="Q41" s="7" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="R41" s="7">
         <v>2</v>
       </c>
       <c r="S41" s="7" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="T41" s="7" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="U41" s="7" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
     </row>
     <row r="42">
       <c r="B42" s="6" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="C42" s="6" t="s">
+        <v>288</v>
+      </c>
+      <c r="D42" s="6" t="s">
         <v>283</v>
       </c>
-      <c r="D42" s="6" t="s">
-        <v>278</v>
-      </c>
       <c r="E42" s="6">
         <v>2</v>
       </c>
       <c r="F42" s="6" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="I42" s="6" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="J42" s="6" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="K42" s="6">
         <v>584</v>
@@ -4300,48 +4350,48 @@
         <v>15000</v>
       </c>
       <c r="Q42" s="6" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="R42" s="6">
         <v>2</v>
       </c>
       <c r="S42" s="6" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="T42" s="6" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="U42" s="6" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
     </row>
     <row r="43">
       <c r="B43" s="7" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="D43" s="7" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="E43" s="7">
         <v>1</v>
       </c>
       <c r="F43" s="7" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="G43" s="7" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="H43" s="7" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="I43" s="7" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="J43" s="7" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="K43" s="7">
         <v>372</v>
@@ -4362,48 +4412,48 @@
         <v>15000</v>
       </c>
       <c r="Q43" s="7" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="R43" s="7">
         <v>2</v>
       </c>
       <c r="S43" s="7" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="T43" s="7" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="U43" s="7" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
     </row>
     <row r="44">
       <c r="B44" s="6" t="s">
+        <v>299</v>
+      </c>
+      <c r="C44" s="6" t="s">
+        <v>300</v>
+      </c>
+      <c r="D44" s="6" t="s">
         <v>294</v>
       </c>
-      <c r="C44" s="6" t="s">
-        <v>295</v>
-      </c>
-      <c r="D44" s="6" t="s">
-        <v>289</v>
-      </c>
       <c r="E44" s="6">
         <v>2</v>
       </c>
       <c r="F44" s="6" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="I44" s="6" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="J44" s="6" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="K44" s="6">
         <v>670</v>
@@ -4424,48 +4474,48 @@
         <v>15000</v>
       </c>
       <c r="Q44" s="6" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="R44" s="6">
         <v>2</v>
       </c>
       <c r="S44" s="6" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="T44" s="6" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="U44" s="6" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
     </row>
     <row r="45">
       <c r="B45" s="7" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="D45" s="7" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="E45" s="7">
         <v>1</v>
       </c>
       <c r="F45" s="7" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="G45" s="7" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="H45" s="7" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="I45" s="7" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="J45" s="7" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="K45" s="7">
         <v>521</v>
@@ -4486,48 +4536,48 @@
         <v>15000</v>
       </c>
       <c r="Q45" s="7" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="R45" s="7">
         <v>1</v>
       </c>
       <c r="S45" s="7" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="T45" s="7" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="U45" s="7" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
     </row>
     <row r="46">
       <c r="B46" s="6" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="E46" s="6">
         <v>1</v>
       </c>
       <c r="F46" s="6" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="I46" s="6" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="J46" s="6" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="K46" s="6">
         <v>400</v>
@@ -4548,48 +4598,48 @@
         <v>17000</v>
       </c>
       <c r="Q46" s="6" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="R46" s="6">
         <v>1</v>
       </c>
       <c r="S46" s="6" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="T46" s="6" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="U46" s="6" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
     </row>
     <row r="47">
       <c r="B47" s="7" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="D47" s="7" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="E47" s="7">
         <v>1</v>
       </c>
       <c r="F47" s="7" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="G47" s="7" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="H47" s="7" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="I47" s="7" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="J47" s="7" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="K47" s="7">
         <v>270</v>
@@ -4610,48 +4660,48 @@
         <v>15000</v>
       </c>
       <c r="Q47" s="7" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="R47" s="7">
         <v>1</v>
       </c>
       <c r="S47" s="7" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="T47" s="7" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="U47" s="7" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
     </row>
     <row r="48">
       <c r="B48" s="6" t="s">
+        <v>325</v>
+      </c>
+      <c r="C48" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="D48" s="6" t="s">
+        <v>327</v>
+      </c>
+      <c r="E48" s="6">
+        <v>1</v>
+      </c>
+      <c r="F48" s="6" t="s">
+        <v>328</v>
+      </c>
+      <c r="G48" s="6" t="s">
         <v>320</v>
       </c>
-      <c r="C48" s="6" t="s">
+      <c r="H48" s="6" t="s">
         <v>321</v>
       </c>
-      <c r="D48" s="6" t="s">
-        <v>322</v>
-      </c>
-      <c r="E48" s="6">
-        <v>1</v>
-      </c>
-      <c r="F48" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="G48" s="6" t="s">
-        <v>315</v>
-      </c>
-      <c r="H48" s="6" t="s">
-        <v>316</v>
-      </c>
       <c r="I48" s="6" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="J48" s="6" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="K48" s="6">
         <v>290</v>
@@ -4672,48 +4722,48 @@
         <v>17000</v>
       </c>
       <c r="Q48" s="6" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="R48" s="6">
         <v>2</v>
       </c>
       <c r="S48" s="6" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="T48" s="6" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="U48" s="6" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
     </row>
     <row r="49">
       <c r="B49" s="7" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="C49" s="7" t="s">
+        <v>332</v>
+      </c>
+      <c r="D49" s="7" t="s">
         <v>327</v>
       </c>
-      <c r="D49" s="7" t="s">
-        <v>322</v>
-      </c>
       <c r="E49" s="7">
         <v>2</v>
       </c>
       <c r="F49" s="7" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="G49" s="7" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="H49" s="7" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="I49" s="7" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="J49" s="7" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="K49" s="7">
         <v>522</v>
@@ -4734,48 +4784,48 @@
         <v>17000</v>
       </c>
       <c r="Q49" s="7" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="R49" s="7">
         <v>2</v>
       </c>
       <c r="S49" s="7" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="T49" s="7" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="U49" s="7" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
     </row>
     <row r="50">
       <c r="B50" s="6" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="E50" s="6">
         <v>1</v>
       </c>
       <c r="F50" s="6" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="I50" s="6" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="J50" s="6" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="K50" s="6">
         <v>310</v>
@@ -4796,48 +4846,48 @@
         <v>15000</v>
       </c>
       <c r="Q50" s="6" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="R50" s="6">
         <v>3</v>
       </c>
       <c r="S50" s="6" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="T50" s="6" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="U50" s="6" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
     </row>
     <row r="51">
       <c r="B51" s="7" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="C51" s="7" t="s">
+        <v>343</v>
+      </c>
+      <c r="D51" s="7" t="s">
         <v>338</v>
       </c>
-      <c r="D51" s="7" t="s">
-        <v>333</v>
-      </c>
       <c r="E51" s="7">
         <v>2</v>
       </c>
       <c r="F51" s="7" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="G51" s="7" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="H51" s="7" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="I51" s="7" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="J51" s="7" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="K51" s="7">
         <v>559</v>
@@ -4858,48 +4908,48 @@
         <v>15000</v>
       </c>
       <c r="Q51" s="7" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="R51" s="7">
         <v>3</v>
       </c>
       <c r="S51" s="7" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="T51" s="7" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="U51" s="7" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
     </row>
     <row r="52">
       <c r="B52" s="6" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="E52" s="6">
         <v>3</v>
       </c>
       <c r="F52" s="6" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="I52" s="6" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="J52" s="6" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="K52" s="6">
         <v>984</v>
@@ -4920,48 +4970,48 @@
         <v>15000</v>
       </c>
       <c r="Q52" s="6" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="R52" s="6">
         <v>3</v>
       </c>
       <c r="S52" s="6" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="T52" s="6" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="U52" s="6" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
     </row>
     <row r="53">
       <c r="B53" s="7" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="D53" s="7" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="E53" s="7">
         <v>1</v>
       </c>
       <c r="F53" s="7" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="G53" s="7" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="H53" s="7" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="I53" s="7" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="J53" s="7" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="K53" s="7">
         <v>499</v>
@@ -4982,48 +5032,48 @@
         <v>15000</v>
       </c>
       <c r="Q53" s="7" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="R53" s="7">
         <v>2</v>
       </c>
       <c r="S53" s="7" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="T53" s="7" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="U53" s="7" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
     </row>
     <row r="54">
       <c r="B54" s="6" t="s">
+        <v>358</v>
+      </c>
+      <c r="C54" s="6" t="s">
+        <v>359</v>
+      </c>
+      <c r="D54" s="6" t="s">
         <v>353</v>
       </c>
-      <c r="C54" s="6" t="s">
-        <v>354</v>
-      </c>
-      <c r="D54" s="6" t="s">
-        <v>348</v>
-      </c>
       <c r="E54" s="6">
         <v>2</v>
       </c>
       <c r="F54" s="6" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="I54" s="6" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="J54" s="6" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="K54" s="6">
         <v>898</v>
@@ -5044,48 +5094,48 @@
         <v>15000</v>
       </c>
       <c r="Q54" s="6" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="R54" s="6">
         <v>2</v>
       </c>
       <c r="S54" s="6" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="T54" s="6" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="U54" s="6" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
     </row>
     <row r="55">
       <c r="B55" s="7" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="D55" s="7" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="E55" s="7">
         <v>1</v>
       </c>
       <c r="F55" s="7" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="G55" s="7" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="H55" s="7" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="I55" s="7" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="J55" s="7" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="K55" s="7">
         <v>465</v>
@@ -5106,48 +5156,48 @@
         <v>15000</v>
       </c>
       <c r="Q55" s="7" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="R55" s="7">
         <v>2</v>
       </c>
       <c r="S55" s="7" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="T55" s="7" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="U55" s="7" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
     </row>
     <row r="56">
       <c r="B56" s="6" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="C56" s="6" t="s">
+        <v>370</v>
+      </c>
+      <c r="D56" s="6" t="s">
         <v>365</v>
       </c>
-      <c r="D56" s="6" t="s">
-        <v>360</v>
-      </c>
       <c r="E56" s="6">
         <v>2</v>
       </c>
       <c r="F56" s="6" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="I56" s="6" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="J56" s="6" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="K56" s="6">
         <v>837</v>
@@ -5168,48 +5218,48 @@
         <v>15000</v>
       </c>
       <c r="Q56" s="6" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="R56" s="6">
         <v>2</v>
       </c>
       <c r="S56" s="6" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="T56" s="6" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="U56" s="6" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
     </row>
     <row r="57">
       <c r="B57" s="7" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="C57" s="7" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="D57" s="7" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="E57" s="7">
         <v>1</v>
       </c>
       <c r="F57" s="7" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="G57" s="7" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="H57" s="7" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="I57" s="7" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="J57" s="7" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="K57" s="7">
         <v>441</v>
@@ -5230,48 +5280,48 @@
         <v>17000</v>
       </c>
       <c r="Q57" s="7" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="R57" s="7">
         <v>3</v>
       </c>
       <c r="S57" s="7" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="T57" s="7" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="U57" s="7" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
     </row>
     <row r="58">
       <c r="B58" s="6" t="s">
+        <v>381</v>
+      </c>
+      <c r="C58" s="6" t="s">
+        <v>382</v>
+      </c>
+      <c r="D58" s="6" t="s">
         <v>376</v>
       </c>
-      <c r="C58" s="6" t="s">
-        <v>377</v>
-      </c>
-      <c r="D58" s="6" t="s">
-        <v>371</v>
-      </c>
       <c r="E58" s="6">
         <v>2</v>
       </c>
       <c r="F58" s="6" t="s">
+        <v>383</v>
+      </c>
+      <c r="G58" s="6" t="s">
+        <v>320</v>
+      </c>
+      <c r="H58" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="I58" s="6" t="s">
         <v>378</v>
       </c>
-      <c r="G58" s="6" t="s">
-        <v>315</v>
-      </c>
-      <c r="H58" s="6" t="s">
-        <v>316</v>
-      </c>
-      <c r="I58" s="6" t="s">
-        <v>373</v>
-      </c>
       <c r="J58" s="6" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="K58" s="6">
         <v>794</v>
@@ -5292,48 +5342,48 @@
         <v>17000</v>
       </c>
       <c r="Q58" s="6" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="R58" s="6">
         <v>3</v>
       </c>
       <c r="S58" s="6" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="T58" s="6" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="U58" s="6" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
     </row>
     <row r="59">
       <c r="B59" s="7" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="D59" s="7" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="E59" s="7">
         <v>3</v>
       </c>
       <c r="F59" s="7" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="G59" s="7" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="H59" s="7" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="I59" s="7" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="J59" s="7" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="K59" s="7">
         <v>1398</v>
@@ -5354,19 +5404,19 @@
         <v>17000</v>
       </c>
       <c r="Q59" s="7" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="R59" s="7">
         <v>3</v>
       </c>
       <c r="S59" s="7" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="T59" s="7" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="U59" s="7" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
     </row>
   </sheetData>
@@ -5389,10 +5439,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
@@ -5406,13 +5456,13 @@
         <v>3</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
     </row>
     <row r="3">
@@ -5420,13 +5470,13 @@
         <v>25</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="E3" s="4" t="s">
         <v>28</v>
@@ -5437,44 +5487,44 @@
         <v>39</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
     </row>
     <row r="6">
       <c r="B6" s="6" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E6" s="6">
         <v>1</v>
@@ -5482,13 +5532,13 @@
     </row>
     <row r="7">
       <c r="B7" s="7" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E7" s="7">
         <v>1</v>
@@ -5496,13 +5546,13 @@
     </row>
     <row r="8">
       <c r="B8" s="6" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E8" s="6">
         <v>1</v>
@@ -5510,13 +5560,13 @@
     </row>
     <row r="9">
       <c r="B9" s="7" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E9" s="7">
         <v>1</v>
@@ -5524,13 +5574,13 @@
     </row>
     <row r="10">
       <c r="B10" s="6" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E10" s="6">
         <v>2</v>
@@ -5538,13 +5588,13 @@
     </row>
     <row r="11">
       <c r="B11" s="7" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E11" s="7">
         <v>2</v>
@@ -5552,13 +5602,13 @@
     </row>
     <row r="12">
       <c r="B12" s="6" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E12" s="6">
         <v>2</v>
@@ -5566,13 +5616,13 @@
     </row>
     <row r="13">
       <c r="B13" s="7" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E13" s="7">
         <v>2</v>
@@ -5580,13 +5630,13 @@
     </row>
     <row r="14">
       <c r="B14" s="6" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="E14" s="6">
         <v>2</v>
@@ -5594,13 +5644,13 @@
     </row>
     <row r="15">
       <c r="B15" s="7" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E15" s="7">
         <v>3</v>
@@ -5608,13 +5658,13 @@
     </row>
     <row r="16">
       <c r="B16" s="6" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E16" s="6">
         <v>3</v>
@@ -5622,13 +5672,13 @@
     </row>
     <row r="17">
       <c r="B17" s="7" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E17" s="7">
         <v>3</v>
@@ -5636,13 +5686,13 @@
     </row>
     <row r="18">
       <c r="B18" s="6" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E18" s="6">
         <v>3</v>
@@ -5650,13 +5700,13 @@
     </row>
     <row r="19">
       <c r="B19" s="7" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E19" s="7">
         <v>3</v>
@@ -5664,13 +5714,13 @@
     </row>
     <row r="20">
       <c r="B20" s="6" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="E20" s="6">
         <v>3</v>
@@ -5678,13 +5728,13 @@
     </row>
     <row r="21">
       <c r="B21" s="7" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E21" s="7">
         <v>1</v>
@@ -5692,13 +5742,13 @@
     </row>
     <row r="22">
       <c r="B22" s="6" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E22" s="6">
         <v>1</v>
@@ -5706,13 +5756,13 @@
     </row>
     <row r="23">
       <c r="B23" s="7" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E23" s="7">
         <v>1</v>
@@ -5720,13 +5770,13 @@
     </row>
     <row r="24">
       <c r="B24" s="6" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E24" s="6">
         <v>1</v>
@@ -5734,13 +5784,13 @@
     </row>
     <row r="25">
       <c r="B25" s="7" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E25" s="7">
         <v>1</v>
@@ -5748,13 +5798,13 @@
     </row>
     <row r="26">
       <c r="B26" s="6" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E26" s="6">
         <v>1</v>
@@ -5762,13 +5812,13 @@
     </row>
     <row r="27">
       <c r="B27" s="7" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E27" s="7">
         <v>1</v>
@@ -5776,13 +5826,13 @@
     </row>
     <row r="28">
       <c r="B28" s="6" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E28" s="6">
         <v>1</v>
@@ -5790,13 +5840,13 @@
     </row>
     <row r="29">
       <c r="B29" s="7" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E29" s="7">
         <v>2</v>
@@ -5804,13 +5854,13 @@
     </row>
     <row r="30">
       <c r="B30" s="6" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E30" s="6">
         <v>2</v>
@@ -5818,13 +5868,13 @@
     </row>
     <row r="31">
       <c r="B31" s="7" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E31" s="7">
         <v>2</v>
@@ -5832,13 +5882,13 @@
     </row>
     <row r="32">
       <c r="B32" s="6" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E32" s="6">
         <v>2</v>
@@ -5846,13 +5896,13 @@
     </row>
     <row r="33">
       <c r="B33" s="7" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="E33" s="7">
         <v>2</v>
@@ -5860,13 +5910,13 @@
     </row>
     <row r="34">
       <c r="B34" s="6" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E34" s="6">
         <v>1</v>
@@ -5874,13 +5924,13 @@
     </row>
     <row r="35">
       <c r="B35" s="7" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E35" s="7">
         <v>1</v>
@@ -5888,13 +5938,13 @@
     </row>
     <row r="36">
       <c r="B36" s="6" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E36" s="6">
         <v>1</v>
@@ -5902,13 +5952,13 @@
     </row>
     <row r="37">
       <c r="B37" s="7" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E37" s="7">
         <v>1</v>
@@ -5916,13 +5966,13 @@
     </row>
     <row r="38">
       <c r="B38" s="6" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E38" s="6">
         <v>2</v>
@@ -5930,13 +5980,13 @@
     </row>
     <row r="39">
       <c r="B39" s="7" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="D39" s="7" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E39" s="7">
         <v>2</v>
@@ -5944,13 +5994,13 @@
     </row>
     <row r="40">
       <c r="B40" s="6" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E40" s="6">
         <v>2</v>
@@ -5958,13 +6008,13 @@
     </row>
     <row r="41">
       <c r="B41" s="7" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="D41" s="7" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E41" s="7">
         <v>2</v>
@@ -5972,13 +6022,13 @@
     </row>
     <row r="42">
       <c r="B42" s="6" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="E42" s="6">
         <v>2</v>
@@ -5986,13 +6036,13 @@
     </row>
     <row r="43">
       <c r="B43" s="7" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="D43" s="7" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E43" s="7">
         <v>1</v>
@@ -6000,13 +6050,13 @@
     </row>
     <row r="44">
       <c r="B44" s="6" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E44" s="6">
         <v>1</v>
@@ -6014,13 +6064,13 @@
     </row>
     <row r="45">
       <c r="B45" s="7" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="D45" s="7" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E45" s="7">
         <v>1</v>
@@ -6028,13 +6078,13 @@
     </row>
     <row r="46">
       <c r="B46" s="6" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E46" s="6">
         <v>1</v>
@@ -6042,13 +6092,13 @@
     </row>
     <row r="47">
       <c r="B47" s="7" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="D47" s="7" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E47" s="7">
         <v>1</v>
@@ -6056,13 +6106,13 @@
     </row>
     <row r="48">
       <c r="B48" s="6" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E48" s="6">
         <v>1</v>
@@ -6070,13 +6120,13 @@
     </row>
     <row r="49">
       <c r="B49" s="7" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="D49" s="7" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E49" s="7">
         <v>1</v>
@@ -6084,13 +6134,13 @@
     </row>
     <row r="50">
       <c r="B50" s="6" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E50" s="6">
         <v>1</v>
@@ -6098,13 +6148,13 @@
     </row>
     <row r="51">
       <c r="B51" s="7" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="D51" s="7" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E51" s="7">
         <v>2</v>
@@ -6112,13 +6162,13 @@
     </row>
     <row r="52">
       <c r="B52" s="6" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E52" s="6">
         <v>2</v>
@@ -6126,13 +6176,13 @@
     </row>
     <row r="53">
       <c r="B53" s="7" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="D53" s="7" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E53" s="7">
         <v>2</v>
@@ -6140,13 +6190,13 @@
     </row>
     <row r="54">
       <c r="B54" s="6" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E54" s="6">
         <v>2</v>
@@ -6154,13 +6204,13 @@
     </row>
     <row r="55">
       <c r="B55" s="7" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="D55" s="7" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="E55" s="7">
         <v>2</v>
@@ -6168,13 +6218,13 @@
     </row>
     <row r="56">
       <c r="B56" s="6" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="D56" s="6" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E56" s="6">
         <v>1</v>
@@ -6182,13 +6232,13 @@
     </row>
     <row r="57">
       <c r="B57" s="7" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="C57" s="7" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="D57" s="7" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E57" s="7">
         <v>1</v>
@@ -6196,13 +6246,13 @@
     </row>
     <row r="58">
       <c r="B58" s="6" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E58" s="6">
         <v>1</v>
@@ -6210,13 +6260,13 @@
     </row>
     <row r="59">
       <c r="B59" s="7" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="D59" s="7" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E59" s="7">
         <v>1</v>
@@ -6224,13 +6274,13 @@
     </row>
     <row r="60">
       <c r="B60" s="6" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="D60" s="6" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E60" s="6">
         <v>2</v>
@@ -6238,13 +6288,13 @@
     </row>
     <row r="61">
       <c r="B61" s="7" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="C61" s="7" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="D61" s="7" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E61" s="7">
         <v>2</v>
@@ -6252,13 +6302,13 @@
     </row>
     <row r="62">
       <c r="B62" s="6" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="C62" s="6" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="D62" s="6" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E62" s="6">
         <v>2</v>
@@ -6266,13 +6316,13 @@
     </row>
     <row r="63">
       <c r="B63" s="7" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="C63" s="7" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="D63" s="7" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E63" s="7">
         <v>2</v>
@@ -6280,13 +6330,13 @@
     </row>
     <row r="64">
       <c r="B64" s="6" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="C64" s="6" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="D64" s="6" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="E64" s="6">
         <v>2</v>
@@ -6294,13 +6344,13 @@
     </row>
     <row r="65">
       <c r="B65" s="7" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="C65" s="7" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="D65" s="7" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E65" s="7">
         <v>3</v>
@@ -6308,13 +6358,13 @@
     </row>
     <row r="66">
       <c r="B66" s="6" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="C66" s="6" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="D66" s="6" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E66" s="6">
         <v>3</v>
@@ -6322,13 +6372,13 @@
     </row>
     <row r="67">
       <c r="B67" s="7" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="C67" s="7" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="D67" s="7" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E67" s="7">
         <v>3</v>
@@ -6336,13 +6386,13 @@
     </row>
     <row r="68">
       <c r="B68" s="6" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="C68" s="6" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E68" s="6">
         <v>3</v>
@@ -6350,13 +6400,13 @@
     </row>
     <row r="69">
       <c r="B69" s="7" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="C69" s="7" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="D69" s="7" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E69" s="7">
         <v>3</v>
@@ -6364,13 +6414,13 @@
     </row>
     <row r="70">
       <c r="B70" s="6" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="C70" s="6" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="D70" s="6" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="E70" s="6">
         <v>3</v>
@@ -6378,13 +6428,13 @@
     </row>
     <row r="71">
       <c r="B71" s="7" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="C71" s="7" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="D71" s="7" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E71" s="7">
         <v>1</v>
@@ -6392,13 +6442,13 @@
     </row>
     <row r="72">
       <c r="B72" s="6" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="C72" s="6" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="D72" s="6" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E72" s="6">
         <v>1</v>
@@ -6406,13 +6456,13 @@
     </row>
     <row r="73">
       <c r="B73" s="7" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="C73" s="7" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="D73" s="7" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E73" s="7">
         <v>1</v>
@@ -6420,13 +6470,13 @@
     </row>
     <row r="74">
       <c r="B74" s="6" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="C74" s="6" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="D74" s="6" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E74" s="6">
         <v>1</v>
@@ -6434,13 +6484,13 @@
     </row>
     <row r="75">
       <c r="B75" s="7" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="C75" s="7" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="D75" s="7" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E75" s="7">
         <v>1</v>
@@ -6448,13 +6498,13 @@
     </row>
     <row r="76">
       <c r="B76" s="6" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="C76" s="6" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="D76" s="6" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E76" s="6">
         <v>1</v>
@@ -6462,13 +6512,13 @@
     </row>
     <row r="77">
       <c r="B77" s="7" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="C77" s="7" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="D77" s="7" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E77" s="7">
         <v>1</v>
@@ -6476,13 +6526,13 @@
     </row>
     <row r="78">
       <c r="B78" s="6" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="C78" s="6" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="D78" s="6" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E78" s="6">
         <v>1</v>
@@ -6490,13 +6540,13 @@
     </row>
     <row r="79">
       <c r="B79" s="7" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="C79" s="7" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="D79" s="7" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E79" s="7">
         <v>2</v>
@@ -6504,13 +6554,13 @@
     </row>
     <row r="80">
       <c r="B80" s="6" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="C80" s="6" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="D80" s="6" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E80" s="6">
         <v>2</v>
@@ -6518,13 +6568,13 @@
     </row>
     <row r="81">
       <c r="B81" s="7" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="C81" s="7" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="D81" s="7" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E81" s="7">
         <v>2</v>
@@ -6532,13 +6582,13 @@
     </row>
     <row r="82">
       <c r="B82" s="6" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="C82" s="6" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="D82" s="6" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E82" s="6">
         <v>2</v>
@@ -6546,13 +6596,13 @@
     </row>
     <row r="83">
       <c r="B83" s="7" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="C83" s="7" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="D83" s="7" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="E83" s="7">
         <v>2</v>
@@ -6560,13 +6610,13 @@
     </row>
     <row r="84">
       <c r="B84" s="6" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="C84" s="6" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="D84" s="6" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E84" s="6">
         <v>1</v>
@@ -6574,13 +6624,13 @@
     </row>
     <row r="85">
       <c r="B85" s="7" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="C85" s="7" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="D85" s="7" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E85" s="7">
         <v>1</v>
@@ -6588,13 +6638,13 @@
     </row>
     <row r="86">
       <c r="B86" s="6" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="C86" s="6" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="D86" s="6" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E86" s="6">
         <v>1</v>
@@ -6602,13 +6652,13 @@
     </row>
     <row r="87">
       <c r="B87" s="7" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="C87" s="7" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="D87" s="7" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E87" s="7">
         <v>1</v>
@@ -6616,13 +6666,13 @@
     </row>
     <row r="88">
       <c r="B88" s="6" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="C88" s="6" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="D88" s="6" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E88" s="6">
         <v>1</v>
@@ -6630,13 +6680,13 @@
     </row>
     <row r="89">
       <c r="B89" s="7" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="C89" s="7" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="D89" s="7" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E89" s="7">
         <v>1</v>
@@ -6644,13 +6694,13 @@
     </row>
     <row r="90">
       <c r="B90" s="6" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="C90" s="6" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="D90" s="6" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E90" s="6">
         <v>1</v>
@@ -6658,13 +6708,13 @@
     </row>
     <row r="91">
       <c r="B91" s="7" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="C91" s="7" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="D91" s="7" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E91" s="7">
         <v>1</v>
@@ -6672,13 +6722,13 @@
     </row>
     <row r="92">
       <c r="B92" s="6" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="C92" s="6" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="D92" s="6" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E92" s="6">
         <v>2</v>
@@ -6686,13 +6736,13 @@
     </row>
     <row r="93">
       <c r="B93" s="7" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="C93" s="7" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="D93" s="7" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E93" s="7">
         <v>2</v>
@@ -6700,13 +6750,13 @@
     </row>
     <row r="94">
       <c r="B94" s="6" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="C94" s="6" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="D94" s="6" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E94" s="6">
         <v>2</v>
@@ -6714,13 +6764,13 @@
     </row>
     <row r="95">
       <c r="B95" s="7" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="C95" s="7" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="D95" s="7" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E95" s="7">
         <v>2</v>
@@ -6728,13 +6778,13 @@
     </row>
     <row r="96">
       <c r="B96" s="6" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="C96" s="6" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="D96" s="6" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="E96" s="6">
         <v>2</v>
@@ -6742,13 +6792,13 @@
     </row>
     <row r="97">
       <c r="B97" s="7" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="C97" s="7" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="D97" s="7" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E97" s="7">
         <v>1</v>
@@ -6756,13 +6806,13 @@
     </row>
     <row r="98">
       <c r="B98" s="6" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="C98" s="6" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="D98" s="6" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E98" s="6">
         <v>1</v>
@@ -6770,13 +6820,13 @@
     </row>
     <row r="99">
       <c r="B99" s="7" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="C99" s="7" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="D99" s="7" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E99" s="7">
         <v>1</v>
@@ -6784,13 +6834,13 @@
     </row>
     <row r="100">
       <c r="B100" s="6" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="C100" s="6" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="D100" s="6" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E100" s="6">
         <v>1</v>
@@ -6798,13 +6848,13 @@
     </row>
     <row r="101">
       <c r="B101" s="7" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="C101" s="7" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="D101" s="7" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E101" s="7">
         <v>1</v>
@@ -6812,13 +6862,13 @@
     </row>
     <row r="102">
       <c r="B102" s="6" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="C102" s="6" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="D102" s="6" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E102" s="6">
         <v>1</v>
@@ -6826,13 +6876,13 @@
     </row>
     <row r="103">
       <c r="B103" s="7" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="C103" s="7" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="D103" s="7" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E103" s="7">
         <v>1</v>
@@ -6840,13 +6890,13 @@
     </row>
     <row r="104">
       <c r="B104" s="6" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="C104" s="6" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="D104" s="6" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E104" s="6">
         <v>1</v>
@@ -6854,13 +6904,13 @@
     </row>
     <row r="105">
       <c r="B105" s="7" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="C105" s="7" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="D105" s="7" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E105" s="7">
         <v>2</v>
@@ -6868,13 +6918,13 @@
     </row>
     <row r="106">
       <c r="B106" s="6" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="C106" s="6" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="D106" s="6" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E106" s="6">
         <v>2</v>
@@ -6882,13 +6932,13 @@
     </row>
     <row r="107">
       <c r="B107" s="7" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="C107" s="7" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="D107" s="7" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E107" s="7">
         <v>2</v>
@@ -6896,13 +6946,13 @@
     </row>
     <row r="108">
       <c r="B108" s="6" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="C108" s="6" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="D108" s="6" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E108" s="6">
         <v>2</v>
@@ -6910,13 +6960,13 @@
     </row>
     <row r="109">
       <c r="B109" s="7" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="C109" s="7" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="D109" s="7" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="E109" s="7">
         <v>2</v>
@@ -6924,13 +6974,13 @@
     </row>
     <row r="110">
       <c r="B110" s="6" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="C110" s="6" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="D110" s="6" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E110" s="6">
         <v>3</v>
@@ -6938,13 +6988,13 @@
     </row>
     <row r="111">
       <c r="B111" s="7" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="C111" s="7" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="D111" s="7" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E111" s="7">
         <v>3</v>
@@ -6952,13 +7002,13 @@
     </row>
     <row r="112">
       <c r="B112" s="6" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="C112" s="6" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="D112" s="6" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E112" s="6">
         <v>3</v>
@@ -6966,13 +7016,13 @@
     </row>
     <row r="113">
       <c r="B113" s="7" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="C113" s="7" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="D113" s="7" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E113" s="7">
         <v>3</v>
@@ -6980,13 +7030,13 @@
     </row>
     <row r="114">
       <c r="B114" s="6" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="C114" s="6" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="D114" s="6" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E114" s="6">
         <v>3</v>
@@ -6994,13 +7044,13 @@
     </row>
     <row r="115">
       <c r="B115" s="7" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="C115" s="7" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="D115" s="7" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="E115" s="7">
         <v>3</v>
@@ -7008,13 +7058,13 @@
     </row>
     <row r="116">
       <c r="B116" s="6" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="C116" s="6" t="s">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="D116" s="6" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E116" s="6">
         <v>1</v>
@@ -7022,13 +7072,13 @@
     </row>
     <row r="117">
       <c r="B117" s="7" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="C117" s="7" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="D117" s="7" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E117" s="7">
         <v>1</v>
@@ -7036,13 +7086,13 @@
     </row>
     <row r="118">
       <c r="B118" s="6" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="C118" s="6" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="D118" s="6" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E118" s="6">
         <v>1</v>
@@ -7050,13 +7100,13 @@
     </row>
     <row r="119">
       <c r="B119" s="7" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="C119" s="7" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="D119" s="7" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E119" s="7">
         <v>1</v>
@@ -7064,13 +7114,13 @@
     </row>
     <row r="120">
       <c r="B120" s="6" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="C120" s="6" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="D120" s="6" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E120" s="6">
         <v>1</v>
@@ -7078,13 +7128,13 @@
     </row>
     <row r="121">
       <c r="B121" s="7" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="C121" s="7" t="s">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="D121" s="7" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E121" s="7">
         <v>1</v>
@@ -7092,13 +7142,13 @@
     </row>
     <row r="122">
       <c r="B122" s="6" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="C122" s="6" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="D122" s="6" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E122" s="6">
         <v>1</v>
@@ -7106,13 +7156,13 @@
     </row>
     <row r="123">
       <c r="B123" s="7" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="C123" s="7" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="D123" s="7" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E123" s="7">
         <v>1</v>
@@ -7120,13 +7170,13 @@
     </row>
     <row r="124">
       <c r="B124" s="6" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="C124" s="6" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="D124" s="6" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E124" s="6">
         <v>2</v>
@@ -7134,13 +7184,13 @@
     </row>
     <row r="125">
       <c r="B125" s="7" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="C125" s="7" t="s">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="D125" s="7" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E125" s="7">
         <v>2</v>
@@ -7148,13 +7198,13 @@
     </row>
     <row r="126">
       <c r="B126" s="6" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="C126" s="6" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="D126" s="6" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E126" s="6">
         <v>2</v>
@@ -7162,13 +7212,13 @@
     </row>
     <row r="127">
       <c r="B127" s="7" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="C127" s="7" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="D127" s="7" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E127" s="7">
         <v>2</v>
@@ -7176,13 +7226,13 @@
     </row>
     <row r="128">
       <c r="B128" s="6" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="C128" s="6" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="D128" s="6" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="E128" s="6">
         <v>2</v>
@@ -7190,13 +7240,13 @@
     </row>
     <row r="129">
       <c r="B129" s="7" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="C129" s="7" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="D129" s="7" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E129" s="7">
         <v>1</v>
@@ -7204,13 +7254,13 @@
     </row>
     <row r="130">
       <c r="B130" s="6" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="C130" s="6" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="D130" s="6" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E130" s="6">
         <v>1</v>
@@ -7218,13 +7268,13 @@
     </row>
     <row r="131">
       <c r="B131" s="7" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="C131" s="7" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="D131" s="7" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E131" s="7">
         <v>1</v>
@@ -7232,13 +7282,13 @@
     </row>
     <row r="132">
       <c r="B132" s="6" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="C132" s="6" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="D132" s="6" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E132" s="6">
         <v>1</v>
@@ -7246,13 +7296,13 @@
     </row>
     <row r="133">
       <c r="B133" s="7" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="C133" s="7" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="D133" s="7" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E133" s="7">
         <v>1</v>
@@ -7260,13 +7310,13 @@
     </row>
     <row r="134">
       <c r="B134" s="6" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="C134" s="6" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="D134" s="6" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E134" s="6">
         <v>1</v>
@@ -7274,13 +7324,13 @@
     </row>
     <row r="135">
       <c r="B135" s="7" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="C135" s="7" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="D135" s="7" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E135" s="7">
         <v>1</v>
@@ -7288,13 +7338,13 @@
     </row>
     <row r="136">
       <c r="B136" s="6" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="C136" s="6" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="D136" s="6" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E136" s="6">
         <v>1</v>
@@ -7302,13 +7352,13 @@
     </row>
     <row r="137">
       <c r="B137" s="7" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="C137" s="7" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="D137" s="7" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E137" s="7">
         <v>2</v>
@@ -7316,13 +7366,13 @@
     </row>
     <row r="138">
       <c r="B138" s="6" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="C138" s="6" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="D138" s="6" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E138" s="6">
         <v>2</v>
@@ -7330,13 +7380,13 @@
     </row>
     <row r="139">
       <c r="B139" s="7" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="C139" s="7" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="D139" s="7" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E139" s="7">
         <v>2</v>
@@ -7344,13 +7394,13 @@
     </row>
     <row r="140">
       <c r="B140" s="6" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="C140" s="6" t="s">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="D140" s="6" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E140" s="6">
         <v>2</v>
@@ -7358,13 +7408,13 @@
     </row>
     <row r="141">
       <c r="B141" s="7" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="C141" s="7" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="D141" s="7" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="E141" s="7">
         <v>2</v>
@@ -7372,13 +7422,13 @@
     </row>
     <row r="142">
       <c r="B142" s="6" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="C142" s="6" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="D142" s="6" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E142" s="6">
         <v>1</v>
@@ -7386,13 +7436,13 @@
     </row>
     <row r="143">
       <c r="B143" s="7" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="C143" s="7" t="s">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="D143" s="7" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E143" s="7">
         <v>1</v>
@@ -7400,13 +7450,13 @@
     </row>
     <row r="144">
       <c r="B144" s="6" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="C144" s="6" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="D144" s="6" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E144" s="6">
         <v>1</v>
@@ -7414,13 +7464,13 @@
     </row>
     <row r="145">
       <c r="B145" s="7" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="C145" s="7" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="D145" s="7" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E145" s="7">
         <v>1</v>
@@ -7428,13 +7478,13 @@
     </row>
     <row r="146">
       <c r="B146" s="6" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="C146" s="6" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="D146" s="6" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E146" s="6">
         <v>1</v>
@@ -7442,13 +7492,13 @@
     </row>
     <row r="147">
       <c r="B147" s="7" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="C147" s="7" t="s">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="D147" s="7" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E147" s="7">
         <v>1</v>
@@ -7456,13 +7506,13 @@
     </row>
     <row r="148">
       <c r="B148" s="6" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="C148" s="6" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="D148" s="6" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E148" s="6">
         <v>1</v>
@@ -7470,13 +7520,13 @@
     </row>
     <row r="149">
       <c r="B149" s="7" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="C149" s="7" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="D149" s="7" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E149" s="7">
         <v>1</v>
@@ -7484,13 +7534,13 @@
     </row>
     <row r="150">
       <c r="B150" s="6" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="C150" s="6" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="D150" s="6" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E150" s="6">
         <v>1</v>
@@ -7498,13 +7548,13 @@
     </row>
     <row r="151">
       <c r="B151" s="7" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="C151" s="7" t="s">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="D151" s="7" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E151" s="7">
         <v>1</v>
@@ -7512,13 +7562,13 @@
     </row>
     <row r="152">
       <c r="B152" s="6" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="C152" s="6" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="D152" s="6" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E152" s="6">
         <v>1</v>
@@ -7526,13 +7576,13 @@
     </row>
     <row r="153">
       <c r="B153" s="7" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="C153" s="7" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="D153" s="7" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E153" s="7">
         <v>1</v>
@@ -7540,13 +7590,13 @@
     </row>
     <row r="154">
       <c r="B154" s="6" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="C154" s="6" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="D154" s="6" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E154" s="6">
         <v>2</v>
@@ -7554,13 +7604,13 @@
     </row>
     <row r="155">
       <c r="B155" s="7" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="C155" s="7" t="s">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="D155" s="7" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E155" s="7">
         <v>2</v>
@@ -7568,13 +7618,13 @@
     </row>
     <row r="156">
       <c r="B156" s="6" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="C156" s="6" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="D156" s="6" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E156" s="6">
         <v>2</v>
@@ -7582,13 +7632,13 @@
     </row>
     <row r="157">
       <c r="B157" s="7" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="C157" s="7" t="s">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="D157" s="7" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E157" s="7">
         <v>2</v>
@@ -7596,13 +7646,13 @@
     </row>
     <row r="158">
       <c r="B158" s="6" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="C158" s="6" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="D158" s="6" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="E158" s="6">
         <v>2</v>
@@ -7610,13 +7660,13 @@
     </row>
     <row r="159">
       <c r="B159" s="7" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="C159" s="7" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="D159" s="7" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E159" s="7">
         <v>3</v>
@@ -7624,13 +7674,13 @@
     </row>
     <row r="160">
       <c r="B160" s="6" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="C160" s="6" t="s">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="D160" s="6" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E160" s="6">
         <v>3</v>
@@ -7638,13 +7688,13 @@
     </row>
     <row r="161">
       <c r="B161" s="7" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="C161" s="7" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="D161" s="7" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E161" s="7">
         <v>3</v>
@@ -7652,13 +7702,13 @@
     </row>
     <row r="162">
       <c r="B162" s="6" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="C162" s="6" t="s">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="D162" s="6" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E162" s="6">
         <v>3</v>
@@ -7666,13 +7716,13 @@
     </row>
     <row r="163">
       <c r="B163" s="7" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="C163" s="7" t="s">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="D163" s="7" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E163" s="7">
         <v>3</v>
@@ -7680,13 +7730,13 @@
     </row>
     <row r="164">
       <c r="B164" s="6" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="C164" s="6" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="D164" s="6" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="E164" s="6">
         <v>3</v>
@@ -7694,13 +7744,13 @@
     </row>
     <row r="165">
       <c r="B165" s="7" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="C165" s="7" t="s">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="D165" s="7" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E165" s="7">
         <v>1</v>
@@ -7708,13 +7758,13 @@
     </row>
     <row r="166">
       <c r="B166" s="6" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="C166" s="6" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="D166" s="6" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E166" s="6">
         <v>1</v>
@@ -7722,13 +7772,13 @@
     </row>
     <row r="167">
       <c r="B167" s="7" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="C167" s="7" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="D167" s="7" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E167" s="7">
         <v>1</v>
@@ -7736,13 +7786,13 @@
     </row>
     <row r="168">
       <c r="B168" s="6" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="C168" s="6" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="D168" s="6" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E168" s="6">
         <v>1</v>
@@ -7750,13 +7800,13 @@
     </row>
     <row r="169">
       <c r="B169" s="7" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="C169" s="7" t="s">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="D169" s="7" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E169" s="7">
         <v>2</v>
@@ -7764,13 +7814,13 @@
     </row>
     <row r="170">
       <c r="B170" s="6" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="C170" s="6" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="D170" s="6" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E170" s="6">
         <v>2</v>
@@ -7778,13 +7828,13 @@
     </row>
     <row r="171">
       <c r="B171" s="7" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="C171" s="7" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="D171" s="7" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E171" s="7">
         <v>2</v>
@@ -7792,13 +7842,13 @@
     </row>
     <row r="172">
       <c r="B172" s="6" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="C172" s="6" t="s">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="D172" s="6" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E172" s="6">
         <v>2</v>
@@ -7806,13 +7856,13 @@
     </row>
     <row r="173">
       <c r="B173" s="7" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="C173" s="7" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="D173" s="7" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="E173" s="7">
         <v>2</v>
@@ -7820,13 +7870,13 @@
     </row>
     <row r="174">
       <c r="B174" s="6" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="C174" s="6" t="s">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="D174" s="6" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E174" s="6">
         <v>1</v>
@@ -7834,13 +7884,13 @@
     </row>
     <row r="175">
       <c r="B175" s="7" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="C175" s="7" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="D175" s="7" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E175" s="7">
         <v>1</v>
@@ -7848,13 +7898,13 @@
     </row>
     <row r="176">
       <c r="B176" s="6" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="C176" s="6" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="D176" s="6" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E176" s="6">
         <v>1</v>
@@ -7862,13 +7912,13 @@
     </row>
     <row r="177">
       <c r="B177" s="7" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="C177" s="7" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="D177" s="7" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E177" s="7">
         <v>1</v>
@@ -7876,13 +7926,13 @@
     </row>
     <row r="178">
       <c r="B178" s="6" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="C178" s="6" t="s">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="D178" s="6" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E178" s="6">
         <v>2</v>
@@ -7890,13 +7940,13 @@
     </row>
     <row r="179">
       <c r="B179" s="7" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="C179" s="7" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="D179" s="7" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E179" s="7">
         <v>2</v>
@@ -7904,13 +7954,13 @@
     </row>
     <row r="180">
       <c r="B180" s="6" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="C180" s="6" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="D180" s="6" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E180" s="6">
         <v>2</v>
@@ -7918,13 +7968,13 @@
     </row>
     <row r="181">
       <c r="B181" s="7" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="C181" s="7" t="s">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="D181" s="7" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E181" s="7">
         <v>2</v>
@@ -7932,13 +7982,13 @@
     </row>
     <row r="182">
       <c r="B182" s="6" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="C182" s="6" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="D182" s="6" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="E182" s="6">
         <v>2</v>
@@ -7946,13 +7996,13 @@
     </row>
     <row r="183">
       <c r="B183" s="7" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="C183" s="7" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="D183" s="7" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E183" s="7">
         <v>1</v>
@@ -7960,13 +8010,13 @@
     </row>
     <row r="184">
       <c r="B184" s="6" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="C184" s="6" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="D184" s="6" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E184" s="6">
         <v>1</v>
@@ -7974,13 +8024,13 @@
     </row>
     <row r="185">
       <c r="B185" s="7" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="C185" s="7" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="D185" s="7" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E185" s="7">
         <v>1</v>
@@ -7988,13 +8038,13 @@
     </row>
     <row r="186">
       <c r="B186" s="6" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="C186" s="6" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="D186" s="6" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E186" s="6">
         <v>1</v>
@@ -8002,13 +8052,13 @@
     </row>
     <row r="187">
       <c r="B187" s="7" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="C187" s="7" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="D187" s="7" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E187" s="7">
         <v>1</v>
@@ -8016,13 +8066,13 @@
     </row>
     <row r="188">
       <c r="B188" s="6" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="C188" s="6" t="s">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="D188" s="6" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E188" s="6">
         <v>1</v>
@@ -8030,13 +8080,13 @@
     </row>
     <row r="189">
       <c r="B189" s="7" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="C189" s="7" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="D189" s="7" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E189" s="7">
         <v>1</v>
@@ -8044,13 +8094,13 @@
     </row>
     <row r="190">
       <c r="B190" s="6" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="C190" s="6" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="D190" s="6" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E190" s="6">
         <v>1</v>
@@ -8058,13 +8108,13 @@
     </row>
     <row r="191">
       <c r="B191" s="7" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="C191" s="7" t="s">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="D191" s="7" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E191" s="7">
         <v>1</v>
@@ -8072,13 +8122,13 @@
     </row>
     <row r="192">
       <c r="B192" s="6" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="C192" s="6" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="D192" s="6" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E192" s="6">
         <v>1</v>
@@ -8086,13 +8136,13 @@
     </row>
     <row r="193">
       <c r="B193" s="7" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="C193" s="7" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="D193" s="7" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E193" s="7">
         <v>1</v>
@@ -8100,13 +8150,13 @@
     </row>
     <row r="194">
       <c r="B194" s="6" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="C194" s="6" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="D194" s="6" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E194" s="6">
         <v>1</v>
@@ -8114,13 +8164,13 @@
     </row>
     <row r="195">
       <c r="B195" s="7" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="C195" s="7" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="D195" s="7" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E195" s="7">
         <v>1</v>
@@ -8128,13 +8178,13 @@
     </row>
     <row r="196">
       <c r="B196" s="6" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="C196" s="6" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="D196" s="6" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E196" s="6">
         <v>1</v>
@@ -8142,13 +8192,13 @@
     </row>
     <row r="197">
       <c r="B197" s="7" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="C197" s="7" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="D197" s="7" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E197" s="7">
         <v>1</v>
@@ -8156,13 +8206,13 @@
     </row>
     <row r="198">
       <c r="B198" s="6" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="C198" s="6" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="D198" s="6" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E198" s="6">
         <v>1</v>
@@ -8170,13 +8220,13 @@
     </row>
     <row r="199">
       <c r="B199" s="7" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="C199" s="7" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="D199" s="7" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E199" s="7">
         <v>2</v>
@@ -8184,13 +8234,13 @@
     </row>
     <row r="200">
       <c r="B200" s="6" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="C200" s="6" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="D200" s="6" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E200" s="6">
         <v>2</v>
@@ -8198,13 +8248,13 @@
     </row>
     <row r="201">
       <c r="B201" s="7" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="C201" s="7" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="D201" s="7" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E201" s="7">
         <v>2</v>
@@ -8212,13 +8262,13 @@
     </row>
     <row r="202">
       <c r="B202" s="6" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="C202" s="6" t="s">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="D202" s="6" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E202" s="6">
         <v>2</v>
@@ -8226,13 +8276,13 @@
     </row>
     <row r="203">
       <c r="B203" s="7" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="C203" s="7" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="D203" s="7" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="E203" s="7">
         <v>2</v>
@@ -8240,13 +8290,13 @@
     </row>
     <row r="204">
       <c r="B204" s="6" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="C204" s="6" t="s">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="D204" s="6" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E204" s="6">
         <v>1</v>
@@ -8254,13 +8304,13 @@
     </row>
     <row r="205">
       <c r="B205" s="7" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="C205" s="7" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="D205" s="7" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E205" s="7">
         <v>1</v>
@@ -8268,13 +8318,13 @@
     </row>
     <row r="206">
       <c r="B206" s="6" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="C206" s="6" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="D206" s="6" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E206" s="6">
         <v>1</v>
@@ -8282,13 +8332,13 @@
     </row>
     <row r="207">
       <c r="B207" s="7" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="C207" s="7" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="D207" s="7" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E207" s="7">
         <v>1</v>
@@ -8296,13 +8346,13 @@
     </row>
     <row r="208">
       <c r="B208" s="6" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="C208" s="6" t="s">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="D208" s="6" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E208" s="6">
         <v>2</v>
@@ -8310,13 +8360,13 @@
     </row>
     <row r="209">
       <c r="B209" s="7" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="C209" s="7" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="D209" s="7" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E209" s="7">
         <v>2</v>
@@ -8324,13 +8374,13 @@
     </row>
     <row r="210">
       <c r="B210" s="6" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="C210" s="6" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="D210" s="6" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E210" s="6">
         <v>2</v>
@@ -8338,13 +8388,13 @@
     </row>
     <row r="211">
       <c r="B211" s="7" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="C211" s="7" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="D211" s="7" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E211" s="7">
         <v>2</v>
@@ -8352,13 +8402,13 @@
     </row>
     <row r="212">
       <c r="B212" s="6" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="C212" s="6" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="D212" s="6" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="E212" s="6">
         <v>2</v>
@@ -8366,13 +8416,13 @@
     </row>
     <row r="213">
       <c r="B213" s="7" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="C213" s="7" t="s">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="D213" s="7" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E213" s="7">
         <v>3</v>
@@ -8380,13 +8430,13 @@
     </row>
     <row r="214">
       <c r="B214" s="6" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="C214" s="6" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="D214" s="6" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E214" s="6">
         <v>3</v>
@@ -8394,13 +8444,13 @@
     </row>
     <row r="215">
       <c r="B215" s="7" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="C215" s="7" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="D215" s="7" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E215" s="7">
         <v>3</v>
@@ -8408,13 +8458,13 @@
     </row>
     <row r="216">
       <c r="B216" s="6" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="C216" s="6" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="D216" s="6" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E216" s="6">
         <v>3</v>
@@ -8422,13 +8472,13 @@
     </row>
     <row r="217">
       <c r="B217" s="7" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="C217" s="7" t="s">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="D217" s="7" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E217" s="7">
         <v>3</v>
@@ -8436,13 +8486,13 @@
     </row>
     <row r="218">
       <c r="B218" s="6" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="C218" s="6" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="D218" s="6" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="E218" s="6">
         <v>3</v>
@@ -8450,13 +8500,13 @@
     </row>
     <row r="219">
       <c r="B219" s="7" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="C219" s="7" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="D219" s="7" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E219" s="7">
         <v>1</v>
@@ -8464,13 +8514,13 @@
     </row>
     <row r="220">
       <c r="B220" s="6" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="C220" s="6" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="D220" s="6" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E220" s="6">
         <v>1</v>
@@ -8478,13 +8528,13 @@
     </row>
     <row r="221">
       <c r="B221" s="7" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="C221" s="7" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="D221" s="7" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E221" s="7">
         <v>1</v>
@@ -8492,13 +8542,13 @@
     </row>
     <row r="222">
       <c r="B222" s="6" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="C222" s="6" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="D222" s="6" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E222" s="6">
         <v>1</v>
@@ -8506,13 +8556,13 @@
     </row>
     <row r="223">
       <c r="B223" s="7" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="C223" s="7" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="D223" s="7" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E223" s="7">
         <v>2</v>
@@ -8520,13 +8570,13 @@
     </row>
     <row r="224">
       <c r="B224" s="6" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="C224" s="6" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="D224" s="6" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E224" s="6">
         <v>2</v>
@@ -8534,13 +8584,13 @@
     </row>
     <row r="225">
       <c r="B225" s="7" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="C225" s="7" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="D225" s="7" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E225" s="7">
         <v>2</v>
@@ -8548,13 +8598,13 @@
     </row>
     <row r="226">
       <c r="B226" s="6" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="C226" s="6" t="s">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="D226" s="6" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E226" s="6">
         <v>2</v>
@@ -8562,13 +8612,13 @@
     </row>
     <row r="227">
       <c r="B227" s="7" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="C227" s="7" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="D227" s="7" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="E227" s="7">
         <v>2</v>
@@ -8576,13 +8626,13 @@
     </row>
     <row r="228">
       <c r="B228" s="6" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="C228" s="6" t="s">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="D228" s="6" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E228" s="6">
         <v>1</v>
@@ -8590,13 +8640,13 @@
     </row>
     <row r="229">
       <c r="B229" s="7" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="C229" s="7" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="D229" s="7" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E229" s="7">
         <v>1</v>
@@ -8604,13 +8654,13 @@
     </row>
     <row r="230">
       <c r="B230" s="6" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="C230" s="6" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="D230" s="6" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E230" s="6">
         <v>1</v>
@@ -8618,13 +8668,13 @@
     </row>
     <row r="231">
       <c r="B231" s="7" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="C231" s="7" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="D231" s="7" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E231" s="7">
         <v>1</v>
@@ -8632,13 +8682,13 @@
     </row>
     <row r="232">
       <c r="B232" s="6" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="C232" s="6" t="s">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="D232" s="6" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E232" s="6">
         <v>2</v>
@@ -8646,13 +8696,13 @@
     </row>
     <row r="233">
       <c r="B233" s="7" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="C233" s="7" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="D233" s="7" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E233" s="7">
         <v>2</v>
@@ -8660,13 +8710,13 @@
     </row>
     <row r="234">
       <c r="B234" s="6" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="C234" s="6" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="D234" s="6" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E234" s="6">
         <v>2</v>
@@ -8674,13 +8724,13 @@
     </row>
     <row r="235">
       <c r="B235" s="7" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="C235" s="7" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="D235" s="7" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E235" s="7">
         <v>2</v>
@@ -8688,13 +8738,13 @@
     </row>
     <row r="236">
       <c r="B236" s="6" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="C236" s="6" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="D236" s="6" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="E236" s="6">
         <v>2</v>
@@ -8702,13 +8752,13 @@
     </row>
     <row r="237">
       <c r="B237" s="7" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="C237" s="7" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="D237" s="7" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E237" s="7">
         <v>1</v>
@@ -8716,13 +8766,13 @@
     </row>
     <row r="238">
       <c r="B238" s="6" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="C238" s="6" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="D238" s="6" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E238" s="6">
         <v>1</v>
@@ -8730,13 +8780,13 @@
     </row>
     <row r="239">
       <c r="B239" s="7" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="C239" s="7" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="D239" s="7" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E239" s="7">
         <v>1</v>
@@ -8744,13 +8794,13 @@
     </row>
     <row r="240">
       <c r="B240" s="6" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="C240" s="6" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="D240" s="6" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E240" s="6">
         <v>1</v>
@@ -8758,13 +8808,13 @@
     </row>
     <row r="241">
       <c r="B241" s="7" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="C241" s="7" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="D241" s="7" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E241" s="7">
         <v>2</v>
@@ -8772,13 +8822,13 @@
     </row>
     <row r="242">
       <c r="B242" s="6" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="C242" s="6" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="D242" s="6" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E242" s="6">
         <v>2</v>
@@ -8786,13 +8836,13 @@
     </row>
     <row r="243">
       <c r="B243" s="7" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="C243" s="7" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="D243" s="7" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E243" s="7">
         <v>2</v>
@@ -8800,13 +8850,13 @@
     </row>
     <row r="244">
       <c r="B244" s="6" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="C244" s="6" t="s">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="D244" s="6" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E244" s="6">
         <v>2</v>
@@ -8814,13 +8864,13 @@
     </row>
     <row r="245">
       <c r="B245" s="7" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="C245" s="7" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="D245" s="7" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="E245" s="7">
         <v>2</v>
@@ -8828,13 +8878,13 @@
     </row>
     <row r="246">
       <c r="B246" s="6" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="C246" s="6" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="D246" s="6" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E246" s="6">
         <v>3</v>
@@ -8842,13 +8892,13 @@
     </row>
     <row r="247">
       <c r="B247" s="7" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="C247" s="7" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="D247" s="7" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E247" s="7">
         <v>3</v>
@@ -8856,13 +8906,13 @@
     </row>
     <row r="248">
       <c r="B248" s="6" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="C248" s="6" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="D248" s="6" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E248" s="6">
         <v>3</v>
@@ -8870,13 +8920,13 @@
     </row>
     <row r="249">
       <c r="B249" s="7" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="C249" s="7" t="s">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="D249" s="7" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E249" s="7">
         <v>3</v>
@@ -8884,13 +8934,13 @@
     </row>
     <row r="250">
       <c r="B250" s="6" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="C250" s="6" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="D250" s="6" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E250" s="6">
         <v>3</v>
@@ -8898,13 +8948,13 @@
     </row>
     <row r="251">
       <c r="B251" s="7" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="C251" s="7" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="D251" s="7" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="E251" s="7">
         <v>3</v>
@@ -8935,10 +8985,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
@@ -8955,34 +9005,34 @@
         <v>2</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>453</v>
+        <v>458</v>
       </c>
     </row>
     <row r="3">
@@ -8990,34 +9040,34 @@
         <v>25</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
     </row>
     <row r="4">
@@ -9025,67 +9075,77 @@
         <v>39</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>459</v>
-      </c>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
+        <v>464</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>465</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>466</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>467</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>468</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>469</v>
+      </c>
       <c r="J4" s="4" t="s">
-        <v>460</v>
+        <v>470</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>461</v>
+        <v>471</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
     </row>
     <row r="6">
       <c r="B6" s="6" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="D6" s="6">
         <v>336</v>
@@ -9106,23 +9166,23 @@
         <v>0</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>462</v>
+        <v>472</v>
       </c>
       <c r="K6" s="6" t="s">
-        <v>463</v>
+        <v>473</v>
       </c>
     </row>
     <row r="7">
       <c r="K7" s="7" t="s">
-        <v>464</v>
+        <v>474</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="6" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="D8" s="6">
         <v>575</v>
@@ -9143,28 +9203,28 @@
         <v>0</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>465</v>
+        <v>475</v>
       </c>
       <c r="K8" s="6" t="s">
-        <v>466</v>
+        <v>476</v>
       </c>
     </row>
     <row r="9">
       <c r="K9" s="7" t="s">
-        <v>467</v>
+        <v>477</v>
       </c>
     </row>
     <row r="10">
       <c r="K10" s="6" t="s">
-        <v>468</v>
+        <v>478</v>
       </c>
     </row>
     <row r="11">
       <c r="B11" s="7" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="D11" s="7">
         <v>258</v>
@@ -9185,23 +9245,23 @@
         <v>0</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>469</v>
+        <v>479</v>
       </c>
       <c r="K11" s="7" t="s">
-        <v>470</v>
+        <v>480</v>
       </c>
     </row>
     <row r="12">
       <c r="K12" s="6" t="s">
-        <v>464</v>
+        <v>474</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="7" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="D13" s="7">
         <v>386</v>
@@ -9222,23 +9282,23 @@
         <v>0</v>
       </c>
       <c r="J13" s="7" t="s">
-        <v>471</v>
+        <v>481</v>
       </c>
       <c r="K13" s="7" t="s">
-        <v>470</v>
+        <v>480</v>
       </c>
     </row>
     <row r="14">
       <c r="K14" s="6" t="s">
-        <v>464</v>
+        <v>474</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="7" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="D15" s="7">
         <v>413</v>
@@ -9259,23 +9319,23 @@
         <v>0</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>472</v>
+        <v>482</v>
       </c>
       <c r="K15" s="7" t="s">
-        <v>473</v>
+        <v>483</v>
       </c>
     </row>
     <row r="16">
       <c r="K16" s="6" t="s">
-        <v>464</v>
+        <v>474</v>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="7" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="D17" s="7">
         <v>258</v>
@@ -9296,23 +9356,23 @@
         <v>0</v>
       </c>
       <c r="J17" s="7" t="s">
-        <v>474</v>
+        <v>484</v>
       </c>
       <c r="K17" s="7" t="s">
-        <v>470</v>
+        <v>480</v>
       </c>
     </row>
     <row r="18">
       <c r="K18" s="6" t="s">
-        <v>464</v>
+        <v>474</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="7" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="D19" s="7">
         <v>441</v>
@@ -9333,28 +9393,28 @@
         <v>0</v>
       </c>
       <c r="J19" s="7" t="s">
-        <v>475</v>
+        <v>485</v>
       </c>
       <c r="K19" s="7" t="s">
-        <v>476</v>
+        <v>486</v>
       </c>
     </row>
     <row r="20">
       <c r="K20" s="6" t="s">
-        <v>467</v>
+        <v>477</v>
       </c>
     </row>
     <row r="21">
       <c r="K21" s="7" t="s">
-        <v>468</v>
+        <v>478</v>
       </c>
     </row>
     <row r="22">
       <c r="B22" s="6" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="D22" s="6">
         <v>336</v>
@@ -9375,23 +9435,23 @@
         <v>0</v>
       </c>
       <c r="J22" s="6" t="s">
-        <v>477</v>
+        <v>487</v>
       </c>
       <c r="K22" s="6" t="s">
-        <v>463</v>
+        <v>473</v>
       </c>
     </row>
     <row r="23">
       <c r="K23" s="7" t="s">
-        <v>464</v>
+        <v>474</v>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="6" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="D24" s="6">
         <v>444</v>
@@ -9412,23 +9472,23 @@
         <v>0</v>
       </c>
       <c r="J24" s="6" t="s">
-        <v>478</v>
+        <v>488</v>
       </c>
       <c r="K24" s="6" t="s">
-        <v>479</v>
+        <v>489</v>
       </c>
     </row>
     <row r="25">
       <c r="K25" s="7" t="s">
-        <v>464</v>
+        <v>474</v>
       </c>
     </row>
     <row r="26">
       <c r="B26" s="6" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="D26" s="6">
         <v>317</v>
@@ -9449,23 +9509,23 @@
         <v>0</v>
       </c>
       <c r="J26" s="6" t="s">
-        <v>480</v>
+        <v>490</v>
       </c>
       <c r="K26" s="6" t="s">
-        <v>479</v>
+        <v>489</v>
       </c>
     </row>
     <row r="27">
       <c r="K27" s="7" t="s">
-        <v>464</v>
+        <v>474</v>
       </c>
     </row>
     <row r="28">
       <c r="B28" s="6" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="D28" s="6">
         <v>542</v>
@@ -9486,28 +9546,28 @@
         <v>0</v>
       </c>
       <c r="J28" s="6" t="s">
-        <v>481</v>
+        <v>491</v>
       </c>
       <c r="K28" s="6" t="s">
-        <v>482</v>
+        <v>492</v>
       </c>
     </row>
     <row r="29">
       <c r="K29" s="7" t="s">
-        <v>467</v>
+        <v>477</v>
       </c>
     </row>
     <row r="30">
       <c r="K30" s="6" t="s">
-        <v>468</v>
+        <v>478</v>
       </c>
     </row>
     <row r="31">
       <c r="B31" s="7" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="D31" s="7">
         <v>336</v>
@@ -9528,23 +9588,23 @@
         <v>0</v>
       </c>
       <c r="J31" s="7" t="s">
-        <v>483</v>
+        <v>493</v>
       </c>
       <c r="K31" s="7" t="s">
-        <v>463</v>
+        <v>473</v>
       </c>
     </row>
     <row r="32">
       <c r="K32" s="6" t="s">
-        <v>464</v>
+        <v>474</v>
       </c>
     </row>
     <row r="33">
       <c r="B33" s="7" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="D33" s="7">
         <v>258</v>
@@ -9565,23 +9625,23 @@
         <v>0</v>
       </c>
       <c r="J33" s="7" t="s">
-        <v>484</v>
+        <v>494</v>
       </c>
       <c r="K33" s="7" t="s">
-        <v>470</v>
+        <v>480</v>
       </c>
     </row>
     <row r="34">
       <c r="K34" s="6" t="s">
-        <v>464</v>
+        <v>474</v>
       </c>
     </row>
     <row r="35">
       <c r="B35" s="7" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="D35" s="7">
         <v>242</v>
@@ -9602,23 +9662,23 @@
         <v>0</v>
       </c>
       <c r="J35" s="7" t="s">
-        <v>485</v>
+        <v>495</v>
       </c>
       <c r="K35" s="7" t="s">
-        <v>470</v>
+        <v>480</v>
       </c>
     </row>
     <row r="36">
       <c r="K36" s="6" t="s">
-        <v>464</v>
+        <v>474</v>
       </c>
     </row>
     <row r="37">
       <c r="B37" s="7" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="D37" s="7">
         <v>414</v>
@@ -9639,28 +9699,28 @@
         <v>0</v>
       </c>
       <c r="J37" s="7" t="s">
+        <v>496</v>
+      </c>
+      <c r="K37" s="7" t="s">
         <v>486</v>
-      </c>
-      <c r="K37" s="7" t="s">
-        <v>476</v>
       </c>
     </row>
     <row r="38">
       <c r="K38" s="6" t="s">
-        <v>467</v>
+        <v>477</v>
       </c>
     </row>
     <row r="39">
       <c r="K39" s="7" t="s">
-        <v>468</v>
+        <v>478</v>
       </c>
     </row>
     <row r="40">
       <c r="B40" s="6" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="D40" s="6">
         <v>260</v>
@@ -9681,23 +9741,23 @@
         <v>0</v>
       </c>
       <c r="J40" s="6" t="s">
-        <v>487</v>
+        <v>497</v>
       </c>
       <c r="K40" s="6" t="s">
-        <v>470</v>
+        <v>480</v>
       </c>
     </row>
     <row r="41">
       <c r="K41" s="7" t="s">
-        <v>464</v>
+        <v>474</v>
       </c>
     </row>
     <row r="42">
       <c r="B42" s="6" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="D42" s="6">
         <v>298</v>
@@ -9718,23 +9778,23 @@
         <v>0</v>
       </c>
       <c r="J42" s="6" t="s">
-        <v>488</v>
+        <v>498</v>
       </c>
       <c r="K42" s="6" t="s">
-        <v>479</v>
+        <v>489</v>
       </c>
     </row>
     <row r="43">
       <c r="K43" s="7" t="s">
-        <v>464</v>
+        <v>474</v>
       </c>
     </row>
     <row r="44">
       <c r="B44" s="6" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="D44" s="6">
         <v>232</v>
@@ -9755,23 +9815,23 @@
         <v>0</v>
       </c>
       <c r="J44" s="6" t="s">
-        <v>489</v>
+        <v>499</v>
       </c>
       <c r="K44" s="6" t="s">
-        <v>470</v>
+        <v>480</v>
       </c>
     </row>
     <row r="45">
       <c r="K45" s="7" t="s">
-        <v>464</v>
+        <v>474</v>
       </c>
     </row>
     <row r="46">
       <c r="B46" s="6" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="D46" s="6">
         <v>249</v>
@@ -9792,23 +9852,23 @@
         <v>0</v>
       </c>
       <c r="J46" s="6" t="s">
-        <v>490</v>
+        <v>500</v>
       </c>
       <c r="K46" s="6" t="s">
-        <v>470</v>
+        <v>480</v>
       </c>
     </row>
     <row r="47">
       <c r="K47" s="7" t="s">
-        <v>464</v>
+        <v>474</v>
       </c>
     </row>
     <row r="48">
       <c r="B48" s="6" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="D48" s="6">
         <v>425</v>
@@ -9829,28 +9889,28 @@
         <v>0</v>
       </c>
       <c r="J48" s="6" t="s">
-        <v>491</v>
+        <v>501</v>
       </c>
       <c r="K48" s="6" t="s">
-        <v>476</v>
+        <v>486</v>
       </c>
     </row>
     <row r="49">
       <c r="K49" s="7" t="s">
-        <v>467</v>
+        <v>477</v>
       </c>
     </row>
     <row r="50">
       <c r="K50" s="6" t="s">
-        <v>468</v>
+        <v>478</v>
       </c>
     </row>
     <row r="51">
       <c r="B51" s="7" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="D51" s="7">
         <v>399</v>
@@ -9871,23 +9931,23 @@
         <v>0</v>
       </c>
       <c r="J51" s="7" t="s">
-        <v>492</v>
+        <v>502</v>
       </c>
       <c r="K51" s="7" t="s">
-        <v>479</v>
+        <v>489</v>
       </c>
     </row>
     <row r="52">
       <c r="K52" s="6" t="s">
-        <v>464</v>
+        <v>474</v>
       </c>
     </row>
     <row r="53">
       <c r="B53" s="7" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="D53" s="7">
         <v>372</v>
@@ -9908,23 +9968,23 @@
         <v>0</v>
       </c>
       <c r="J53" s="7" t="s">
-        <v>493</v>
+        <v>503</v>
       </c>
       <c r="K53" s="7" t="s">
-        <v>473</v>
+        <v>483</v>
       </c>
     </row>
     <row r="54">
       <c r="K54" s="6" t="s">
-        <v>464</v>
+        <v>474</v>
       </c>
     </row>
     <row r="55">
       <c r="B55" s="7" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="D55" s="7">
         <v>353</v>
@@ -9945,23 +10005,23 @@
         <v>0</v>
       </c>
       <c r="J55" s="7" t="s">
-        <v>494</v>
+        <v>504</v>
       </c>
       <c r="K55" s="7" t="s">
-        <v>495</v>
+        <v>505</v>
       </c>
     </row>
     <row r="56">
       <c r="K56" s="6" t="s">
-        <v>464</v>
+        <v>474</v>
       </c>
     </row>
     <row r="57">
       <c r="B57" s="7" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="C57" s="7" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="D57" s="7">
         <v>604</v>
@@ -9982,20 +10042,20 @@
         <v>0</v>
       </c>
       <c r="J57" s="7" t="s">
-        <v>496</v>
+        <v>506</v>
       </c>
       <c r="K57" s="7" t="s">
-        <v>497</v>
+        <v>507</v>
       </c>
     </row>
     <row r="58">
       <c r="K58" s="6" t="s">
-        <v>467</v>
+        <v>477</v>
       </c>
     </row>
     <row r="59">
       <c r="K59" s="7" t="s">
-        <v>468</v>
+        <v>478</v>
       </c>
     </row>
   </sheetData>
